--- a/backend/storage/reports/xlsx/MoneyTrace_Analytics_Master_20261010.xlsx
+++ b/backend/storage/reports/xlsx/MoneyTrace_Analytics_Master_20261010.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:24 UTC</t>
+          <t>2026-10-10 18:07 UTC</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:24</t>
+          <t>2026-10-10 18:07</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:24</t>
+          <t>2026-10-10 18:07</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-10 16:24</t>
+          <t>2026-10-10 18:07</t>
         </is>
       </c>
     </row>
